--- a/extenbooks/S1408_extenbook.xlsx
+++ b/extenbooks/S1408_extenbook.xlsx
@@ -4326,7 +4326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:A78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4358,7 +4358,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**DPR · Phase 5 · Ch 14 · Fig 14.17 · Authored 2026-05-18**</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -4368,278 +4368,278 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>**DPR · Phase 5 · Ch 14 · Fig 14.17 · Authored 2026-05-18**</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>## 1. Definition</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HP(100) phase plot: y = nominal-wage growth where `w = EC*100/FEE`, x = intensity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>HP(100) phase plot: y = nominal-wage growth where `w = EC*100/FEE`, x = intensity.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>The original Phillips relation -- but plotted vs unemployment INTENSITY (not</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>the rate). Per Eq. 14.19: nominal-wage Phillips = wage-share Phillips +</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inflation + productivity growth. Table 14.3 secondary regression decomposes</t>
+          <t>The original Phillips relation -- but plotted vs unemployment INTENSITY (not</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>the residual; published era-1 coefficient on inflation is "slightly below 1"</t>
+          <t>the rate). Per Eq. 14.19: nominal-wage Phillips = wage-share Phillips +</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>and on productivity growth ≈ 0.82.</t>
+          <t>inflation + productivity growth. Table 14.3 secondary regression decomposes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>the residual; published era-1 coefficient on inflation is "slightly below 1"</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>and on productivity growth ≈ 0.82.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>| Subseries | Source |</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| S1408-A `GMWAGEHP100` | Appendix 14.3 |</t>
+          <t>| Subseries | Source |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| S1408-B `ulintensityhp100` | Appendix 14.3 |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>| S1408-A `GMWAGEHP100` | Appendix 14.3 |</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| S1408-B `ulintensityhp100` | Appendix 14.3 |</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Direct pass-through. Processor additionally:</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>- Fits two-era Phillips curves (direct refit) at constrained-b=1 and free-b</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>- Runs Table 14.3 OLS `GMWAGEHP100 = const + b_p * inflrateHP100 + b_y *</t>
+          <t>Direct pass-through. Processor additionally:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GPRODVTYHP100` per era</t>
+          <t>- Fits two-era Phillips curves (direct refit) at constrained-b=1 and free-b</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>- Runs Table 14.3 OLS `GMWAGEHP100 = const + b_p * inflrateHP100 + b_y *</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t xml:space="preserve">  GPRODVTYHP100` per era</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1949-2011 (sample window 1949-1982 / 1994-2011 per Appendix 14.2; off-by-one</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>with chapter-text 1948-1982 noted -- differencing loses 1948).</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1949-2011 (sample window 1949-1982 / 1994-2011 per Appendix 14.2; off-by-one</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>with chapter-text 1948-1982 noted -- differencing loses 1948).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>## 6. Units</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Decimal HP100; OLS coefficients dimensionless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>Decimal HP100; OLS coefficients dimensionless.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1. Inherits productivity concept-policing from S1406.</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2. Inherits UEMPMEAN 2011 break from S1402.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3. HP lambda=100.</t>
+          <t>1. Inherits productivity concept-policing from S1406.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4. Sample-window off-by-one: text says 1948-1982; Appendix Stata output and</t>
+          <t>2. Inherits UEMPMEAN 2011 break from S1402.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">   differencing both start at 1949. Phase 5 uses 1949-1982.</t>
+          <t>3. HP lambda=100.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4. Sample-window off-by-one: text says 1948-1982; Appendix Stata output and</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">   differencing both start at 1949. Phase 5 uses 1949-1982.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>## 8. Cross-references</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CD `S075`. Book p. 670-672. Equation 14.19. Table 14.3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>CD `S075`. Book p. 670-672. Equation 14.19. Table 14.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>±1.0% pass-through; Table 14.3 coefficients reported informationally.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4">
+    <row r="53">
+      <c r="A53" s="4">
         <f>== EPR: S1408_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t># S1408 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>**Ch 14 · Authored 2026-05-18**</t>
+          <t># S1408 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4649,125 +4649,135 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>## Classification</t>
+          <t>**Ch 14 · Authored 2026-05-18**</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>`time_series` · `direct`. Extension via re-derivation from S1401 + S1406 +</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S1402 inputs.</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>`time_series` · `direct`. Extension via re-derivation from S1401 + S1406 +</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>## Method (both variants emitted)</t>
+          <t>S1402 inputs.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>- **direct_refit**: fit Phillips form to extended GMWAGEHP100</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- **algebraic_decomposition**: S1405-era-fit + HP100(inflation) +</t>
+          <t>## Method (both variants emitted)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HP100(productivity growth) per Eq. 14.19</t>
+          <t>- **direct_refit**: fit Phillips form to extended GMWAGEHP100</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>- **algebraic_decomposition**: S1405-era-fit + HP100(inflation) +</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t xml:space="preserve">  HP100(productivity growth) per Eq. 14.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Both reported in `S1408_phillips_fits.json` sidecar, alongside the Table 14.3</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>secondary regression results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## Concept policing</t>
+          <t>secondary regression results.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Inherited from S1406 (nominal wage w = EC*100/FEE uses same per-FTE</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>convention).</t>
+          <t>## Concept policing</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Inherited from S1406 (nominal wage w = EC*100/FEE uses same per-FTE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>convention).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>## No-Proxy / No-Synthetic disclosures</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Inherits from S1401, S1402, S1406.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Inherits from S1401, S1402, S1406.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>## CD2 divergence pre-disclosure</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Minor expected.</t>
         </is>
@@ -5130,11 +5140,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5157,76 +5167,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HP(100)-Filtered Rate of Change of Nominal Wages vs Unemployment Intensity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1408_research.json", "adequacy_report": "Technical/docs/chapters/CH14_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1408_DPR.md", "epr": "Technical/docs/series/S1408_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1408_load.py", "processor": "Technical/code/P02_processors/P02_S1408_construct.py", "validator": "Technical/code/V03_validators/V03_S1408_validate.py", "processed": "Technical/data/processed/S1408.parquet", "chopped_csv": "Technical/chopped/S1408.csv", "extenbook_xlsx": "Technical/extenbooks/S1408_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:58:43.529185+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1408_extenbook.xlsx
+++ b/extenbooks/S1408_extenbook.xlsx
@@ -4326,7 +4326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4358,7 +4358,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Data Provenance Record · Ingestion stage · Chapter 14 · Figure 14.17 · Authored 2026-05-18**</t>
         </is>
       </c>
     </row>
@@ -4368,69 +4368,69 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**DPR · Phase 5 · Ch 14 · Fig 14.17 · Authored 2026-05-18**</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HP(100) (Hodrick-Prescott filter, smoothing parameter lambda=100) phase plot: y = nominal-wage growth where `w = EC*100/FEE` (FEE = full-time-equivalent employees), x = intensity.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>## 1. Definition</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HP(100) phase plot: y = nominal-wage growth where `w = EC*100/FEE`, x = intensity.</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>The original Phillips relation -- but plotted vs unemployment INTENSITY (not</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>the rate). Per Eq. 14.19: nominal-wage Phillips = wage-share Phillips +</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The original Phillips relation -- but plotted vs unemployment INTENSITY (not</t>
+          <t>inflation + productivity growth. Table 14.3 secondary regression decomposes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>the rate). Per Eq. 14.19: nominal-wage Phillips = wage-share Phillips +</t>
+          <t>the residual; published era-1 coefficient on inflation is "slightly below 1"</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inflation + productivity growth. Table 14.3 secondary regression decomposes</t>
+          <t>and on productivity growth ≈ 0.82.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>the residual; published era-1 coefficient on inflation is "slightly below 1"</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>and on productivity growth ≈ 0.82.</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
@@ -4440,344 +4440,347 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1408-A, S1408-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>| Subseries | Source |</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>| Subseries | Source |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| S1408-A `GMWAGEHP100` | Appendix 14.3 |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>| S1408-A `GMWAGEHP100` | Appendix 14.3 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>| S1408-B `ulintensityhp100` | Appendix 14.3 |</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Direct pass-through. Processor additionally:</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>- Fits two-era Phillips curves (direct refit) at constrained-b=1 and free-b</t>
+          <t>Direct pass-through. The processing step additionally:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>- Runs Table 14.3 OLS `GMWAGEHP100 = const + b_p * inflrateHP100 + b_y *</t>
+          <t>- Fits two-era Phillips curves (direct refit) at constrained-b=1 and free-b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>- Runs Table 14.3 OLS `GMWAGEHP100 = const + b_p * inflrateHP100 + b_y *</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t xml:space="preserve">  GPRODVTYHP100` per era</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1949-2011 (sample window 1949-1982 / 1994-2011 per Appendix 14.2; off-by-one</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>1949-2011 (sample window 1949-1982 / 1994-2011 per Appendix 14.2; off-by-one</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>with chapter-text 1948-1982 noted -- differencing loses 1948).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>## 6. Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Decimal HP100; OLS coefficients dimensionless.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1. Inherits productivity concept-policing from S1406.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2. Inherits UEMPMEAN 2011 break from S1402.</t>
+          <t>1. Inherits productivity concept-policing from S1406.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3. HP lambda=100.</t>
+          <t>2. Inherits UEMPMEAN 2011 break from S1402.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4. Sample-window off-by-one: text says 1948-1982; Appendix Stata output and</t>
+          <t>3. HP lambda=100.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">   differencing both start at 1949. Phase 5 uses 1949-1982.</t>
+          <t>4. Sample-window off-by-one: text says 1948-1982; Appendix Stata output and</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   differencing both start at 1949. This build uses 1949-1982.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CD `S075`. Book p. 670-672. Equation 14.19. Table 14.3.</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Predecessor build: `S075`. Book p. 670-672. Equation 14.19. Table 14.3.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>±1.0% pass-through; Table 14.3 coefficients reported informationally.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4">
+    <row r="54">
+      <c r="A54" s="4">
         <f>== EPR: S1408_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t># S1408 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-    </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>**Ch 14 · Authored 2026-05-18**</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>**Chapter 14 · Authored 2026-05-18**</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>## Classification</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>`time_series` · `direct`. Extension via re-derivation from S1401 + S1406 +</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>`time_series` · `direct`. Extension via re-derivation from S1401 + S1406 +</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>S1402 inputs.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-    </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>## Method (both variants emitted)</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>- **direct_refit**: fit Phillips form to extended GMWAGEHP100</t>
+          <t>## Method (both variants emitted)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>- **algebraic_decomposition**: S1405-era-fit + HP100(inflation) +</t>
+          <t>- **direct_refit**: fit Phillips form to extended GMWAGEHP100</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>- **algebraic_decomposition**: S1405-era-fit + HP100 (the Hodrick-Prescott filter, smoothing parameter lambda=100) of inflation +</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t xml:space="preserve">  HP100(productivity growth) per Eq. 14.19</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-    </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Both reported in `S1408_phillips_fits.json` sidecar, alongside the Table 14.3</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Both reported in `S1408_phillips_fits.json` sidecar, alongside the Table 14.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>secondary regression results.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-    </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>## Concept policing</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Inherited from S1406 (nominal wage w = EC*100/FEE uses same per-FTE</t>
+          <t>## Concept policing</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>Inherited from S1406 (nominal wage w = EC*100/FEE (FEE = full-time-equivalent employees) uses same per-full-time-equivalent (FTE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>convention).</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>## No-Proxy / No-Synthetic disclosures</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>## No-Proxy / No-Synthetic disclosures</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Inherits from S1401, S1402, S1406.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-    </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>## CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
+        <is>
+          <t>## Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Minor expected.</t>
         </is>
@@ -5125,7 +5128,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:19:25.080115+00:00</t>
+          <t>2026-07-02T06:19:23.237963+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1408_extenbook.xlsx
+++ b/extenbooks/S1408_extenbook.xlsx
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:23.237963+00:00</t>
+          <t>2026-07-11T03:44:23.228835+00:00</t>
         </is>
       </c>
     </row>
@@ -5143,11 +5143,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5170,6 +5170,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_14_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.14 Figure 14.17 (HP(100)-Filtered Values, Rate of Change of Nominal Wages versus Unemployment Intensity, United States, 1949-2011) -- the nominal-wage Phillips curve (Eq.14.19 = wage-share curve + inflation + productivity growth). Real data present in chopped CSV (127 points, 2 subseries); book_period_validated; figure number and quotes KB-verified (Fig 14.17 quote verbatim at ch14 KB line 1746/1660; Table 14.3 coefficients cross-checked against Appendix 14.2, ch18 KB line 8527-8595: era-1 1949-1982 inflation 0.963465, productivity 0.836600; era-2 1994-2011 inflation 0.832633, productivity 0.714580 -- match research JSON). NOTE: book TEXT (p.672) states the productivity coefficient as '0.82' while Table 14.3 prints 0.836600; this is Shaikh's own rounding in prose, not a transcription error. Two subseries (nominal-wage growth vs intensity) -- per-subseries split below.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1408_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1408_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nominal-wage Phillips curve per Eq. 14.19; Table 14.3 secondary regression of residual on inflation + productivity growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_hp100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
